--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini. Maman dit : c'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme. Maman dit : merci Sami. Sami ferme le couvercle. Ça fait toc.</t>
+          <t>Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme. Merci Sami. Sami ferme le couvercle. Ça fait toc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini.
+maman|C'est l'heure de ranger. Ranger, c'est mettre dans la caisse.
+narrateur|Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme.
+maman|Merci Sami.
+narrateur|Sami ferme le couvercle. Ça fait toc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après le jeu, que fait Sami ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a rangé. Les peluches sont dans la caisse. Le tapis est libre. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ferme la caisse. Maman lui tend l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Sami ferme le couvercle. Ça fait toc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Après le jeu, que fait Sami ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Sami a rangé. Les peluches sont dans la caisse. Le tapis est libre. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Sami ferme la caisse. Maman lui tend l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sami range les peluches</t>
+          <t>Le pique-nique des peluches</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les peluches font un pique-nique sur le tapis. Quand le jeu s'arrête, Nina les met dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme. Merci Sami. Sami ferme le couvercle. Ça fait toc.</t>
+          <t>La pluie tape sur la vitre. Les gouttes glissent, les unes après les autres. Dans la chambre, une couverture rose est bien chaude. Un ours en peluche attend sur l'oreiller. Il est tout doux. Tu as entendu la pluie, Nina ? Oui, maman. Ça fait tic, tic, tic. On reste au chaud, aujourd'hui. Maman plie des chaussettes près du lit. Ça sent le linge propre. En ce moment même, Nina est sur le tapis. Elle a des peluches. L'ours, un lapin, une petite poule. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. La pluie continue, tout doucement. Puis le jeu est fini. Le pique-nique est fini, Nina. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Nina regarde la caisse près du lit. La caisse est ronde. Elle sent le bois. Nina prend l'ours. Il est doux contre sa joue. Elle le met dans la caisse. Elle prend le lapin. Elle le met dans la caisse. Elle prend la poule. Dans la caisse. Bravo, Nina. Les peluches rentrent dans la caisse. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. Tu as fini de ranger tes jouets ? Encore une tasse, papa. Nina met la dernière tasse. La caisse est pleine. Le tapis est vide. La chambre redevient calme. Merci, Nina. Tu as fait du bon travail. Nina ferme le couvercle. Ça fait toc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini.
-maman|C'est l'heure de ranger. Ranger, c'est mettre dans la caisse.
-narrateur|Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme.
-maman|Merci Sami.
-narrateur|Sami ferme le couvercle. Ça fait toc.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|La pluie tape sur la vitre.
+narrateur|Les gouttes glissent, les unes après les autres.
+narrateur|Dans la chambre, une couverture rose est bien chaude.
+narrateur|Un ours en peluche attend sur l'oreiller.
+narrateur|Il est tout doux.
+maman|Tu as entendu la pluie, Nina ?
+enfant-f|Oui, maman. Ça fait tic, tic, tic.
+papa|On reste au chaud, aujourd'hui.
+narrateur|Maman plie des chaussettes près du lit.
+narrateur|Ça sent le linge propre.
+narrateur|En ce moment même, Nina est sur le tapis.
+narrateur|Elle a des peluches.
+narrateur|L'ours, un lapin, une petite poule.
+narrateur|Nina pose trois tasses en bois.
+narrateur|Les tasses font clic.
+enfant-f|C'est un pique-nique !
+maman|Un pique-nique pour les peluches.
+narrateur|Nina donne une tasse à l'ours.
+narrateur|Elle donne une tasse au lapin.
+narrateur|La poule a la petite tasse.
+papa|Ils sont bien installés.
+narrateur|La pluie continue, tout doucement.
+narrateur|Puis le jeu est fini.
+maman|Le pique-nique est fini, Nina.
+maman|C'est l'heure de ranger.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Nina regarde la caisse près du lit.
+narrateur|La caisse est ronde.
+narrateur|Elle sent le bois.
+narrateur|Nina prend l'ours.
+narrateur|Il est doux contre sa joue.
+narrateur|Elle le met dans la caisse.
+narrateur|Elle prend le lapin.
+narrateur|Elle le met dans la caisse.
+narrateur|Elle prend la poule.
+narrateur|Dans la caisse.
+maman|Bravo, Nina.
+maman|Les peluches rentrent dans la caisse.
+narrateur|Nina prend une tasse en bois.
+narrateur|Clic.
+narrateur|Dans la caisse.
+narrateur|Encore une tasse.
+narrateur|Dans la caisse.
+papa|Tu as fini de ranger tes jouets ?
+enfant-f|Encore une tasse, papa.
+narrateur|Nina met la dernière tasse.
+narrateur|La caisse est pleine.
+narrateur|Le tapis est vide.
+narrateur|La chambre redevient calme.
+maman|Merci, Nina.
+maman|Tu as fait du bon travail.
+narrateur|Nina ferme le couvercle.
+narrateur|Ça fait toc.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Sami ?</t>
+          <t>Après le jeu, que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1560,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait Sami ?</t>
+          <t>narrateur|Après le jeu, que fait Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami a rangé. Les peluches sont dans la caisse. Le tapis est libre. Maman est là.</t>
+          <t>Nina a rangé. Les peluches sont dans la caisse. Les tasses aussi. Le tapis est libre. La chambre est calme, maintenant. Bravo, Nina. Tu as mis les jouets dans la caisse. J'ai rangé. Oui. Ranger, c'est mettre dans la caisse. La pluie tapote encore un peu. Tu as fini de ranger tes jouets ? Oui, papa. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1732,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami a rangé. Les peluches sont dans la caisse. Le tapis est libre. Maman est là.</t>
+          <t>narrateur|Nina a rangé.
+narrateur|Les peluches sont dans la caisse.
+narrateur|Les tasses aussi.
+narrateur|Le tapis est libre.
+maman|La chambre est calme, maintenant.
+papa|Bravo, Nina.
+papa|Tu as mis les jouets dans la caisse.
+enfant-f|J'ai rangé.
+maman|Oui.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|La pluie tapote encore un peu.
+papa|Tu as fini de ranger tes jouets ?
+enfant-f|Oui, papa.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sami ferme la caisse. Maman lui tend l'eau.</t>
+          <t>Nina pousse la caisse près du lit. Le bois glisse un peu sur le tapis. Tu veux un peu d'eau ? Oui, maman. Maman lui tend un verre. Nina boit une gorgée. Les peluches sont bien, dans la caisse. Elles dorment, papa. Oui. Elles se reposent. Nina s'assoit sur le tapis libre. La couverture rose est près d'elle. On reste encore un peu ensemble ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1913,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sami ferme la caisse. Maman lui tend l'eau.</t>
+          <t>narrateur|Nina pousse la caisse près du lit.
+narrateur|Le bois glisse un peu sur le tapis.
+maman|Tu veux un peu d'eau ?
+enfant-f|Oui, maman.
+narrateur|Maman lui tend un verre.
+narrateur|Nina boit une gorgée.
+papa|Les peluches sont bien, dans la caisse.
+enfant-f|Elles dorment, papa.
+maman|Oui. Elles se reposent.
+narrateur|Nina s'assoit sur le tapis libre.
+narrateur|La couverture rose est près d'elle.
+maman|On reste encore un peu ensemble ?
+enfant-f|Oui.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les peluches sont dans la caisse. Bravo. Tu as fait du bon travail. Le pique-nique est rangé. La pluie devient toute petite. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2094,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Les peluches sont dans la caisse.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le pique-nique est rangé.
+narrateur|La pluie devient toute petite.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le pique-nique des peluches</t>
+          <t>Le cacao de Nina</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Les peluches font un pique-nique sur le tapis. Quand le jeu s'arrête, Nina les met dans la caisse.</t>
+          <t>Nina veut un vrai cacao sur le tapis. Les tasses en bois prennent la place. Elle range peluches et tasses dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie tape sur la vitre. Les gouttes glissent, les unes après les autres. Dans la chambre, une couverture rose est bien chaude. Un ours en peluche attend sur l'oreiller. Il est tout doux. Tu as entendu la pluie, Nina ? Oui, maman. Ça fait tic, tic, tic. On reste au chaud, aujourd'hui. Maman plie des chaussettes près du lit. Ça sent le linge propre. En ce moment même, Nina est sur le tapis. Elle a des peluches. L'ours, un lapin, une petite poule. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. La pluie continue, tout doucement. Puis le jeu est fini. Le pique-nique est fini, Nina. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Nina regarde la caisse près du lit. La caisse est ronde. Elle sent le bois. Nina prend l'ours. Il est doux contre sa joue. Elle le met dans la caisse. Elle prend le lapin. Elle le met dans la caisse. Elle prend la poule. Dans la caisse. Bravo, Nina. Les peluches rentrent dans la caisse. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. Tu as fini de ranger tes jouets ? Encore une tasse, papa. Nina met la dernière tasse. La caisse est pleine. Le tapis est vide. La chambre redevient calme. Merci, Nina. Tu as fait du bon travail. Nina ferme le couvercle. Ça fait toc.</t>
+          <t>La boîte à musique joue trois notes. Ding. Ding. Dong. Puis elle se tait. Une chaussette sèche sur le dossier de la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux. C'est l'heure de Nina, sur le tapis. Elle a l'ours, un lapin, une petite poule. Elle pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Il est chaud. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui. Au milieu. Maman entre avec la grande tasse. Ça sent le cacao. Une petite vapeur monte. Nina veut poser la tasse au milieu. Une tasse en bois est déjà là. La patte de l'ours est dessus. Je n'ai pas de place. La vraie tasse n'a nulle part où se poser. Les peluches ont encore leur pique-nique. Je voulais le vrai cacao ici. Il faut un petit rond, au milieu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini. Maman dit : c'est l'heure de &lt;emphasis level="moderate"&gt;ranger&lt;/emphasis&gt;. Ranger, c'est mettre dans la caisse. Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme. Maman dit : merci Sami. Sami ferme le couvercle. Ça fait toc.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boîte à musique joue trois notes. Ding. Ding. Dong. Puis elle se tait. Une chaussette sèche sur le dossier de la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux. C'est l'heure de Nina, sur le tapis. Elle a l'ours, un lapin, une petite poule. Elle pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Il est chaud. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui. Au milieu. Maman entre avec la grande tasse. Ça sent le cacao. Une petite vapeur monte. Nina veut poser la tasse au milieu. Une tasse en bois est déjà là. La patte de l'ours est dessus. Je n'ai pas de place. La vraie tasse n'a nulle part où se poser. Les peluches ont encore leur pique-nique. Je voulais le vrai cacao ici. Il faut un petit rond, au milieu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,20 +1324,20 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La pluie tape sur la vitre.
-narrateur|Les gouttes glissent, les unes après les autres.
-narrateur|Dans la chambre, une couverture rose est bien chaude.
+          <t>narrateur|La boîte à musique joue trois notes.
+narrateur|Ding. Ding. Dong.
+narrateur|Puis elle se tait.
+narrateur|Une chaussette sèche sur le dossier de la chaise.
+narrateur|Elle est encore un peu tiède.
+narrateur|Dehors, les feuilles sont mouillées.
+papa|Il fait frais, ce soir.
+maman|Le cacao est sur le feu.
+narrateur|Dans la chambre, le tapis est épais.
 narrateur|Un ours en peluche attend sur l'oreiller.
 narrateur|Il est tout doux.
-maman|Tu as entendu la pluie, Nina ?
-enfant-f|Oui, maman. Ça fait tic, tic, tic.
-papa|On reste au chaud, aujourd'hui.
-narrateur|Maman plie des chaussettes près du lit.
-narrateur|Ça sent le linge propre.
-narrateur|En ce moment même, Nina est sur le tapis.
-narrateur|Elle a des peluches.
-narrateur|L'ours, un lapin, une petite poule.
-narrateur|Nina pose trois tasses en bois.
+narrateur|C'est l'heure de Nina, sur le tapis.
+narrateur|Elle a l'ours, un lapin, une petite poule.
+narrateur|Elle pose trois tasses en bois.
 narrateur|Les tasses font clic.
 enfant-f|C'est un pique-nique !
 maman|Un pique-nique pour les peluches.
@@ -1345,41 +1345,26 @@
 narrateur|Elle donne une tasse au lapin.
 narrateur|La poule a la petite tasse.
 papa|Ils sont bien installés.
-narrateur|La pluie continue, tout doucement.
-narrateur|Puis le jeu est fini.
-maman|Le pique-nique est fini, Nina.
-maman|C'est l'heure de ranger.
-maman|Ranger, c'est mettre dans la caisse.
-narrateur|Nina regarde la caisse près du lit.
-narrateur|La caisse est ronde.
-narrateur|Elle sent le bois.
-narrateur|Nina prend l'ours.
-narrateur|Il est doux contre sa joue.
-narrateur|Elle le met dans la caisse.
-narrateur|Elle prend le lapin.
-narrateur|Elle le met dans la caisse.
-narrateur|Elle prend la poule.
-narrateur|Dans la caisse.
-maman|Bravo, Nina.
-maman|Les peluches rentrent dans la caisse.
-narrateur|Nina prend une tasse en bois.
-narrateur|Clic.
-narrateur|Dans la caisse.
-narrateur|Encore une tasse.
-narrateur|Dans la caisse.
-papa|Tu as fini de ranger tes jouets ?
-enfant-f|Encore une tasse, papa.
-narrateur|Nina met la dernière tasse.
-narrateur|La caisse est pleine.
-narrateur|Le tapis est vide.
-narrateur|La chambre redevient calme.
-maman|Merci, Nina.
-maman|Tu as fait du bon travail.
-narrateur|Nina ferme le couvercle.
-narrateur|Ça fait toc.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Ils boivent du cacao, papa.
+papa|Du cacao en bois, alors.
+narrateur|Nina souffle au-dessus d'une tasse.
+enfant-f|Ffff. Il est chaud.
+maman|Le vrai cacao arrive bientôt.
+enfant-f|On le boit ici, sur le tapis ?
+maman|Oui. Au milieu.
+narrateur|Maman entre avec la grande tasse.
+narrateur|Ça sent le cacao.
+narrateur|Une petite vapeur monte.
+narrateur|Nina veut poser la tasse au milieu.
+narrateur|Une tasse en bois est déjà là.
+narrateur|La patte de l'ours est dessus.
+enfant-f|Je n'ai pas de place.
+narrateur|La vraie tasse n'a nulle part où se poser.
+papa|Les peluches ont encore leur pique-nique.
+enfant-f|Je voulais le vrai cacao ici.
+maman|Il faut un petit rond, au milieu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1409,7 +1394,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après le jeu, que fait Sami ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après le jeu, que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1424,7 +1409,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | il range</t>
+          <t>ranger | la caisse | dans la caisse | elle range | peluches dans la caisse</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1439,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les peluches dans la caisse. Que fait Sami ?</t>
+          <t>Elle met les peluches dans la caisse. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1563,7 +1548,6 @@
           <t>narrateur|Après le jeu, que fait Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1588,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a rangé. Les peluches sont dans la caisse. Les tasses aussi. Le tapis est libre. La chambre est calme, maintenant. Bravo, Nina. Tu as mis les jouets dans la caisse. J'ai rangé. Oui. Ranger, c'est mettre dans la caisse. La pluie tapote encore un peu. Tu as fini de ranger tes jouets ? Oui, papa. C'est du bon travail.</t>
+          <t>Nina prend l'ours. Il est doux contre sa joue. La caisse ronde est près du lit. Nina glisse l'ours dans la caisse. On va ranger. Tu regardes, depuis la caisse. Elle prend le lapin. Dans la caisse. Elle prend la poule. Dans la caisse. Tu ranges les peluches. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. La dernière tasse aussi. Le milieu du tapis est libre. Pour le vrai cacao. Oui. Un petit rond, juste là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami a rangé. Les peluches sont dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina prend l'ours. Il est doux contre sa joue. La caisse ronde est près du lit. Nina glisse l'ours dans la caisse. On va ranger. Tu regardes, depuis la caisse. Elle prend le lapin. Dans la caisse. Elle prend la poule. Dans la caisse. Tu ranges les peluches. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. La dernière tasse aussi. Le milieu du tapis est libre. Pour le vrai cacao. Oui. Un petit rond, juste là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1732,23 +1716,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a rangé.
-narrateur|Les peluches sont dans la caisse.
-narrateur|Les tasses aussi.
-narrateur|Le tapis est libre.
-maman|La chambre est calme, maintenant.
-papa|Bravo, Nina.
-papa|Tu as mis les jouets dans la caisse.
-enfant-f|J'ai rangé.
-maman|Oui.
-maman|Ranger, c'est mettre dans la caisse.
-narrateur|La pluie tapote encore un peu.
-papa|Tu as fini de ranger tes jouets ?
-enfant-f|Oui, papa.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina prend l'ours.
+narrateur|Il est doux contre sa joue.
+narrateur|La caisse ronde est près du lit.
+narrateur|Nina glisse l'ours dans la caisse.
+maman|On va ranger.
+enfant-f|Tu regardes, depuis la caisse.
+narrateur|Elle prend le lapin.
+narrateur|Dans la caisse.
+narrateur|Elle prend la poule.
+narrateur|Dans la caisse.
+maman|Tu ranges les peluches.
+narrateur|Nina prend une tasse en bois.
+narrateur|Clic. Dans la caisse.
+narrateur|Encore une tasse. Dans la caisse.
+narrateur|La dernière tasse aussi.
+papa|Le milieu du tapis est libre.
+enfant-f|Pour le vrai cacao.
+maman|Oui. Un petit rond, juste là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1773,12 +1760,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina pousse la caisse près du lit. Le bois glisse un peu sur le tapis. Tu veux un peu d'eau ? Oui, maman. Maman lui tend un verre. Nina boit une gorgée. Les peluches sont bien, dans la caisse. Elles dorment, papa. Oui. Elles se reposent. Nina s'assoit sur le tapis libre. La couverture rose est près d'elle. On reste encore un peu ensemble ? Oui. Bravo.</t>
+          <t>Maman pose la grande tasse. Le cacao est chaud. Nina s'assoit au milieu du tapis. Elle souffle. Ffff. Il sent bon. Oui. Tout doux. Nina boit une gorgée. C'est sucré. La chaussette sèche encore sur la chaise. Les peluches se reposent. Dans la caisse. La boîte à musique joue une dernière note. Ding. Elles ont eu leur pique-nique. Et moi, le vrai. Oui. Sur le tapis libre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami ferme la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Maman lui tend l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose la grande tasse. Le cacao est chaud. Nina s'assoit au milieu du tapis. Elle souffle. Ffff. Il sent bon. Oui. Tout doux. Nina boit une gorgée. C'est sucré. La chaussette sèche encore sur la chaise. Les peluches se reposent. Dans la caisse. La boîte à musique joue une dernière note. Ding. Elles ont eu leur pique-nique. Et moi, le vrai. Oui. Sur le tapis libre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1913,23 +1900,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina pousse la caisse près du lit.
-narrateur|Le bois glisse un peu sur le tapis.
-maman|Tu veux un peu d'eau ?
-enfant-f|Oui, maman.
-narrateur|Maman lui tend un verre.
+          <t>narrateur|Maman pose la grande tasse.
+narrateur|Le cacao est chaud.
+narrateur|Nina s'assoit au milieu du tapis.
+narrateur|Elle souffle. Ffff.
+enfant-f|Il sent bon.
+papa|Oui. Tout doux.
 narrateur|Nina boit une gorgée.
-papa|Les peluches sont bien, dans la caisse.
-enfant-f|Elles dorment, papa.
-maman|Oui. Elles se reposent.
-narrateur|Nina s'assoit sur le tapis libre.
-narrateur|La couverture rose est près d'elle.
-maman|On reste encore un peu ensemble ?
-enfant-f|Oui.
-papa|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|C'est sucré.
+narrateur|La chaussette sèche encore sur la chaise.
+maman|Les peluches se reposent.
+enfant-f|Dans la caisse.
+narrateur|La boîte à musique joue une dernière note.
+narrateur|Ding.
+papa|Elles ont eu leur pique-nique.
+enfant-f|Et moi, le vrai.
+maman|Oui. Sur le tapis libre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1954,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les peluches sont dans la caisse. Bravo. Tu as fait du bon travail. Le pique-nique est rangé. La pluie devient toute petite. L'histoire est finie.</t>
+          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,15 +2082,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Les peluches sont dans la caisse.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-papa|Le pique-nique est rangé.
-narrateur|La pluie devient toute petite.
+          <t>enfant-f|J'ai bu le cacao.
+maman|Sur le tapis, au milieu.
+narrateur|Les peluches sont dans la caisse.
+papa|La chambre sent encore le cacao.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2121,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2152,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao. L'histoire est finie.</t>
+          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao. L'histoire est finie.</t>
+          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,8 +2085,7 @@
           <t>enfant-f|J'ai bu le cacao.
 maman|Sur le tapis, au milieu.
 narrateur|Les peluches sont dans la caisse.
-papa|La chambre sent encore le cacao.
-narrateur|L'histoire est finie.</t>
+papa|La chambre sent encore le cacao.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2156,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, fin d'après-midi un peu froide</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre, fin d'après-midi un peu froide</t>
+          <t>chambre, pluie, boîte à musique, fin d'après-midi un peu froide</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut un vrai cacao sur le tapis. Les tasses en bois prennent la place. Elle range peluches et tasses dans la caisse.</t>
+          <t>Nina veut le vrai cacao sur le tapis, avec son ours. L'ours disparaît sous le pique-nique. Elle met tasses et peluches dans la caisse pour chercher. L'ours apparaît sous la poule. Ils boivent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La boîte à musique joue trois notes. Ding. Ding. Dong. Puis elle se tait. Une chaussette sèche sur le dossier de la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux. C'est l'heure de Nina, sur le tapis. Elle a l'ours, un lapin, une petite poule. Elle pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Il est chaud. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui. Au milieu. Maman entre avec la grande tasse. Ça sent le cacao. Une petite vapeur monte. Nina veut poser la tasse au milieu. Une tasse en bois est déjà là. La patte de l'ours est dessus. Je n'ai pas de place. La vraie tasse n'a nulle part où se poser. Les peluches ont encore leur pique-nique. Je voulais le vrai cacao ici. Il faut un petit rond, au milieu.</t>
+          <t>Trois notes sortent de la boîte à musique. Ding. Puis plus rien. Une chaussette sèche sur la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux, un peu chaud. En ce moment, Nina est à genoux. Elle prend l'ours contre sa joue. Toi, tu viens au tapis. Un lapin et une poule attendent déjà. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui, au milieu, tout chaud. Maman entre avec la grande tasse. Ça sent le cacao, tout près. Une petite vapeur monte. Nina cherche un rond pour la tasse. Une tasse en bois est déjà là. La patte du lapin est dessus. L'ours veut le vrai cacao aussi. Où est-il, ton ours ? Nina regarde l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture ? Elle soulève la couverture rose. Rien, seulement le drap tiède. Il est perdu. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Il faut un petit rond, au milieu. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. Je cherche dessous.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La boîte à musique joue trois notes. Ding. Ding. Dong. Puis elle se tait. Une chaussette sèche sur le dossier de la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux. C'est l'heure de Nina, sur le tapis. Elle a l'ours, un lapin, une petite poule. Elle pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Il est chaud. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui. Au milieu. Maman entre avec la grande tasse. Ça sent le cacao. Une petite vapeur monte. Nina veut poser la tasse au milieu. Une tasse en bois est déjà là. La patte de l'ours est dessus. Je n'ai pas de place. La vraie tasse n'a nulle part où se poser. Les peluches ont encore leur pique-nique. Je voulais le vrai cacao ici. Il faut un petit rond, au milieu.</t>
+          <t>Trois notes sortent de la boîte à musique. Ding. Puis plus rien. Une chaussette sèche sur la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux, un peu chaud. En ce moment, Nina est à genoux. Elle prend l'ours contre sa joue. Toi, tu viens au tapis. Un lapin et une poule attendent déjà. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui, au milieu, tout chaud. Maman entre avec la grande tasse. Ça sent le cacao, tout près. Une petite vapeur monte. Nina cherche un rond pour la tasse. Une tasse en bois est déjà là. La patte du lapin est dessus. L'ours veut le vrai cacao aussi. Où est-il, ton ours ? Nina regarde l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture ? Elle soulève la couverture rose. Rien, seulement le drap tiède. Il est perdu. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Il faut un petit rond, au milieu. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. Je cherche dessous.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,20 +1324,22 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La boîte à musique joue trois notes.
-narrateur|Ding. Ding. Dong.
-narrateur|Puis elle se tait.
-narrateur|Une chaussette sèche sur le dossier de la chaise.
+          <t>narrateur|Trois notes sortent de la boîte à musique.
+narrateur|Ding.
+narrateur|Puis plus rien.
+narrateur|Une chaussette sèche sur la chaise.
 narrateur|Elle est encore un peu tiède.
 narrateur|Dehors, les feuilles sont mouillées.
 papa|Il fait frais, ce soir.
 maman|Le cacao est sur le feu.
 narrateur|Dans la chambre, le tapis est épais.
 narrateur|Un ours en peluche attend sur l'oreiller.
-narrateur|Il est tout doux.
-narrateur|C'est l'heure de Nina, sur le tapis.
-narrateur|Elle a l'ours, un lapin, une petite poule.
-narrateur|Elle pose trois tasses en bois.
+narrateur|Il est tout doux, un peu chaud.
+narrateur|En ce moment, Nina est à genoux.
+narrateur|Elle prend l'ours contre sa joue.
+enfant-f|Toi, tu viens au tapis.
+narrateur|Un lapin et une poule attendent déjà.
+narrateur|Nina pose trois tasses en bois.
 narrateur|Les tasses font clic.
 enfant-f|C'est un pique-nique !
 maman|Un pique-nique pour les peluches.
@@ -1348,21 +1350,32 @@
 enfant-f|Ils boivent du cacao, papa.
 papa|Du cacao en bois, alors.
 narrateur|Nina souffle au-dessus d'une tasse.
-enfant-f|Ffff. Il est chaud.
+enfant-f|Ffff.
 maman|Le vrai cacao arrive bientôt.
 enfant-f|On le boit ici, sur le tapis ?
-maman|Oui. Au milieu.
+maman|Oui, au milieu, tout chaud.
 narrateur|Maman entre avec la grande tasse.
-narrateur|Ça sent le cacao.
+narrateur|Ça sent le cacao, tout près.
 narrateur|Une petite vapeur monte.
-narrateur|Nina veut poser la tasse au milieu.
+narrateur|Nina cherche un rond pour la tasse.
 narrateur|Une tasse en bois est déjà là.
-narrateur|La patte de l'ours est dessus.
+narrateur|La patte du lapin est dessus.
+enfant-f|L'ours veut le vrai cacao aussi.
+maman|Où est-il, ton ours ?
+narrateur|Nina regarde l'oreiller.
+narrateur|L'oreiller est plat, vide.
+enfant-f|Il n'est plus sur le lit.
+papa|Sous la couverture ?
+narrateur|Elle soulève la couverture rose.
+narrateur|Rien, seulement le drap tiède.
+enfant-f|Il est perdu.
+narrateur|Les peluches et les tasses couvrent le tapis.
 enfant-f|Je n'ai pas de place.
-narrateur|La vraie tasse n'a nulle part où se poser.
-papa|Les peluches ont encore leur pique-nique.
-enfant-f|Je voulais le vrai cacao ici.
-maman|Il faut un petit rond, au milieu.</t>
+maman|Il faut un petit rond, au milieu.
+narrateur|Nina prend une tasse en bois.
+narrateur|Elle la pose dans la caisse ronde.
+narrateur|Clic.
+enfant-f|Je cherche dessous.</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1402,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Nina ?</t>
+          <t>Nina cherche son ours. Où est-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Nina ?</t>
+          <t>Nina cherche son ours. Où est-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1404,12 +1417,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>l'ours</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | elle range | peluches dans la caisse</t>
+          <t>l'ours | ours | nounours | sous la poule | sous les peluches | dessous</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1424,7 +1437,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les peluches dans la caisse. Que fait Nina ?</t>
+          <t>Elle cherche sous les peluches. Où est l'ours ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1473,7 +1486,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait Nina ?</t>
+          <t>narrateur|Nina cherche son ours.
+narrateur|Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina prend l'ours. Il est doux contre sa joue. La caisse ronde est près du lit. Nina glisse l'ours dans la caisse. On va ranger. Tu regardes, depuis la caisse. Elle prend le lapin. Dans la caisse. Elle prend la poule. Dans la caisse. Tu ranges les peluches. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. La dernière tasse aussi. Le milieu du tapis est libre. Pour le vrai cacao. Oui. Un petit rond, juste là.</t>
+          <t>La deuxième tasse va dans la caisse. Clic. Nina prend le lapin tout doux. Elle le glisse dans la caisse. Tu regardes bien sous les peluches ? Oui, maman. La poule est encore au milieu. Un coin de tapis reparaît. Nina soulève la poule. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci, tu l'as trouvé. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina prend l'ours. Il est doux contre sa joue. La caisse ronde est près du lit. Nina glisse l'ours dans la caisse. On va ranger. Tu regardes, depuis la caisse. Elle prend le lapin. Dans la caisse. Elle prend la poule. Dans la caisse. Tu ranges les peluches. Nina prend une tasse en bois. Clic. Dans la caisse. Encore une tasse. Dans la caisse. La dernière tasse aussi. Le milieu du tapis est libre. Pour le vrai cacao. Oui. Un petit rond, juste là.</t>
+          <t>La deuxième tasse va dans la caisse. Clic. Nina prend le lapin tout doux. Elle le glisse dans la caisse. Tu regardes bien sous les peluches ? Oui, maman. La poule est encore au milieu. Un coin de tapis reparaît. Nina soulève la poule. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci, tu l'as trouvé. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1640,7 +1654,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1716,24 +1730,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina prend l'ours.
-narrateur|Il est doux contre sa joue.
-narrateur|La caisse ronde est près du lit.
-narrateur|Nina glisse l'ours dans la caisse.
-maman|On va ranger.
-enfant-f|Tu regardes, depuis la caisse.
-narrateur|Elle prend le lapin.
-narrateur|Dans la caisse.
-narrateur|Elle prend la poule.
-narrateur|Dans la caisse.
-maman|Tu ranges les peluches.
-narrateur|Nina prend une tasse en bois.
-narrateur|Clic. Dans la caisse.
-narrateur|Encore une tasse. Dans la caisse.
-narrateur|La dernière tasse aussi.
-papa|Le milieu du tapis est libre.
-enfant-f|Pour le vrai cacao.
-maman|Oui. Un petit rond, juste là.</t>
+          <t>narrateur|La deuxième tasse va dans la caisse.
+narrateur|Clic.
+narrateur|Nina prend le lapin tout doux.
+narrateur|Elle le glisse dans la caisse.
+maman|Tu regardes bien sous les peluches ?
+enfant-f|Oui, maman.
+narrateur|La poule est encore au milieu.
+papa|Un coin de tapis reparaît.
+narrateur|Nina soulève la poule.
+narrateur|Un museau brun est dessous.
+enfant-f|Mon ours !
+narrateur|L'ours était sous la poule.
+narrateur|Une tasse en bois l'avait caché.
+narrateur|Nina le serre contre sa joue.
+narrateur|Le poil est chaud, un peu écrasé.
+papa|Merci, tu l'as trouvé.
+enfant-f|Il buvait en dessous.
+maman|Te voilà, petit ours.
+narrateur|La dernière tasse va dans la caisse.
+narrateur|Le tapis a un rond vide, au milieu.
+narrateur|Nina pose l'ours contre son genou.</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la grande tasse. Le cacao est chaud. Nina s'assoit au milieu du tapis. Elle souffle. Ffff. Il sent bon. Oui. Tout doux. Nina boit une gorgée. C'est sucré. La chaussette sèche encore sur la chaise. Les peluches se reposent. Dans la caisse. La boîte à musique joue une dernière note. Ding. Elles ont eu leur pique-nique. Et moi, le vrai. Oui. Sur le tapis libre.</t>
+          <t>Maman pose la vraie tasse au milieu. La vapeur sent le cacao. Il est chaud. On souffle un peu. Nina souffle. Ffff. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu veux encore un peu ? Oui, maman. La pluie tapote plus doucement. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. On est bien, ici.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la grande tasse. Le cacao est chaud. Nina s'assoit au milieu du tapis. Elle souffle. Ffff. Il sent bon. Oui. Tout doux. Nina boit une gorgée. C'est sucré. La chaussette sèche encore sur la chaise. Les peluches se reposent. Dans la caisse. La boîte à musique joue une dernière note. Ding. Elles ont eu leur pique-nique. Et moi, le vrai. Oui. Sur le tapis libre.</t>
+          <t>Maman pose la vraie tasse au milieu. La vapeur sent le cacao. Il est chaud. On souffle un peu. Nina souffle. Ffff. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu veux encore un peu ? Oui, maman. La pluie tapote plus doucement. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. On est bien, ici.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1828,7 +1845,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1900,22 +1917,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose la grande tasse.
-narrateur|Le cacao est chaud.
-narrateur|Nina s'assoit au milieu du tapis.
-narrateur|Elle souffle. Ffff.
-enfant-f|Il sent bon.
-papa|Oui. Tout doux.
-narrateur|Nina boit une gorgée.
-narrateur|C'est sucré.
-narrateur|La chaussette sèche encore sur la chaise.
-maman|Les peluches se reposent.
-enfant-f|Dans la caisse.
-narrateur|La boîte à musique joue une dernière note.
-narrateur|Ding.
-papa|Elles ont eu leur pique-nique.
-enfant-f|Et moi, le vrai.
-maman|Oui. Sur le tapis libre.</t>
+          <t>narrateur|Maman pose la vraie tasse au milieu.
+narrateur|La vapeur sent le cacao.
+enfant-f|Il est chaud.
+papa|On souffle un peu.
+narrateur|Nina souffle.
+narrateur|Ffff.
+narrateur|Elle boit une petite gorgée.
+narrateur|Le cacao est doux, un peu sucré.
+enfant-f|L'ours a une goutte, papa.
+papa|Une toute petite goutte.
+maman|Tu veux encore un peu ?
+enfant-f|Oui, maman.
+narrateur|La pluie tapote plus doucement.
+narrateur|La chaussette sur la chaise est sèche.
+narrateur|Nina tient l'ours d'une main.
+narrateur|De l'autre, elle tient la tasse.
+maman|On est bien, ici.</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao.</t>
+          <t>L'ours a bu du cacao. Toi aussi. Bravo, tu l'as retrouvé. La vapeur s'en va tout doux. Le tapis reste chaud sous les genoux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai bu le cacao. Sur le tapis, au milieu. Les peluches sont dans la caisse. La chambre sent encore le cacao.</t>
+          <t>L'ours a bu du cacao. Toi aussi. Bravo, tu l'as retrouvé. La vapeur s'en va tout doux. Le tapis reste chaud sous les genoux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2003,14 +2021,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2082,10 +2100,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai bu le cacao.
-maman|Sur le tapis, au milieu.
-narrateur|Les peluches sont dans la caisse.
-papa|La chambre sent encore le cacao.</t>
+          <t>enfant-f|L'ours a bu du cacao.
+maman|Toi aussi.
+papa|Bravo, tu l'as retrouvé.
+narrateur|La vapeur s'en va tout doux.
+narrateur|Le tapis reste chaud sous les genoux.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2182,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-02.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut le vrai cacao sur le tapis, avec son ours. L'ours disparaît sous le pique-nique. Elle met tasses et peluches dans la caisse pour chercher. L'ours apparaît sous la poule. Ils boivent.</t>
+          <t>Nina veut le cacao au milieu du tapis, maintenant, pour son ours. Une lune d'étain brille sur la boîte à musique. L'ours disparaît sous le pique-nique. Elle cherche le lit, pousse le tas : rien. Elle refuse de foncer, pose les tasses dans la caisse, suit la lune, trouve l'ours sous la poule. La vapeur du cacao s'accroche à la lune d'étain.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Trois notes sortent de la boîte à musique. Ding. Puis plus rien. Une chaussette sèche sur la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux, un peu chaud. En ce moment, Nina est à genoux. Elle prend l'ours contre sa joue. Toi, tu viens au tapis. Un lapin et une poule attendent déjà. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui, au milieu, tout chaud. Maman entre avec la grande tasse. Ça sent le cacao, tout près. Une petite vapeur monte. Nina cherche un rond pour la tasse. Une tasse en bois est déjà là. La patte du lapin est dessus. L'ours veut le vrai cacao aussi. Où est-il, ton ours ? Nina regarde l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture ? Elle soulève la couverture rose. Rien, seulement le drap tiède. Il est perdu. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Il faut un petit rond, au milieu. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. Je cherche dessous.</t>
+          <t>La vapeur du cacao grimpe l'escalier. Elle entre dans la chambre froide. Sur la vitre, la pluie trace un chemin. La boîte à musique vient de se taire. Un ding reste coincé dans l'air. Sur le couvercle, une lune d'étain. Elle capte un bout de ciel gris. La lumière est basse, un peu bleue. Une chaussette sèche sur la chaise. Elle est un peu tiède. La chambre sent le cacao chaud. Il fait frais, ce soir. Le cacao est sur le feu. Je le veux sur le tapis ! Maintenant, maman. Il va refroidir vite. En ce moment, Nina s'agenouille. Le tapis est épais, un peu froid. Un ours brun attend sur l'oreiller. Toi, tu viens au pique-nique. Elle le pose au milieu du tapis. Un lapin gris la rejoint. Une poule jaune s'installe près de lui. Nina aligne trois tasses en bois. Les tasses font clic. C'est pour le vrai cacao. Il arrive, bien chaud. Vous soufflerez dessus. Nina souffle au-dessus d'une tasse. Ffff. Maman pousse la porte, une grande tasse à la main. Une petite vapeur danse au bord. Pose-la au milieu ! Nina cherche un rond libre. La patte du lapin occupe le centre. L'ours veut le cacao, lui. Où est ton ours, alors ? Nina se tourne vers l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture rose ? Elle soulève la couverture. Rien, seulement le drap tiède. Il est perdu ! Le sourire de Nina disparaît. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Nina pousse le tas d'un bras. Une tasse roule vers la chaise. Le tas retombe, plus mêlé. Ça ne marche pas. Dans sa poitrine, ça se bouscule. L'envie et l'inquiétude se heurtent. Maman s'accroupit à la même hauteur. Tu veux pousser, ou regarder ? Je veux mon ours. Nina baisse les épaules.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Trois notes sortent de la boîte à musique. Ding. Puis plus rien. Une chaussette sèche sur la chaise. Elle est encore un peu tiède. Dehors, les feuilles sont mouillées. Il fait frais, ce soir. Le cacao est sur le feu. Dans la chambre, le tapis est épais. Un ours en peluche attend sur l'oreiller. Il est tout doux, un peu chaud. En ce moment, Nina est à genoux. Elle prend l'ours contre sa joue. Toi, tu viens au tapis. Un lapin et une poule attendent déjà. Nina pose trois tasses en bois. Les tasses font clic. C'est un pique-nique ! Un pique-nique pour les peluches. Nina donne une tasse à l'ours. Elle donne une tasse au lapin. La poule a la petite tasse. Ils sont bien installés. Ils boivent du cacao, papa. Du cacao en bois, alors. Nina souffle au-dessus d'une tasse. Ffff. Le vrai cacao arrive bientôt. On le boit ici, sur le tapis ? Oui, au milieu, tout chaud. Maman entre avec la grande tasse. Ça sent le cacao, tout près. Une petite vapeur monte. Nina cherche un rond pour la tasse. Une tasse en bois est déjà là. La patte du lapin est dessus. L'ours veut le vrai cacao aussi. Où est-il, ton ours ? Nina regarde l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture ? Elle soulève la couverture rose. Rien, seulement le drap tiède. Il est perdu. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Il faut un petit rond, au milieu. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. Je cherche dessous.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vapeur du cacao grimpe l'escalier. Elle entre dans la chambre froide. Sur la vitre, la pluie trace un chemin. La boîte à musique vient de se taire. Un ding reste coincé dans l'air. Sur le couvercle, une &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt;. Elle capte un bout de ciel gris. La lumière est basse, un peu bleue. Une chaussette sèche sur la chaise. Elle est un peu tiède. La chambre sent le cacao chaud. Il fait frais, ce soir. Le cacao est sur le feu. Je le veux sur le tapis ! Maintenant, maman. Il va refroidir vite. En ce moment, Nina s'agenouille. Le tapis est épais, un peu froid. Un ours brun attend sur l'oreiller. Toi, tu viens au pique-nique. Elle le pose au milieu du tapis. Un lapin gris la rejoint. Une poule jaune s'installe près de lui. Nina aligne trois tasses en bois. Les tasses font clic. C'est pour le vrai cacao. Il arrive, bien chaud. Vous soufflerez dessus. Nina souffle au-dessus d'une tasse. Ffff. Maman pousse la porte, une grande tasse à la main. Une petite vapeur danse au bord. Pose-la au milieu ! Nina cherche un rond libre. La patte du lapin occupe le centre. L'ours veut le cacao, lui. Où est ton ours, alors ? Nina se tourne vers l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture rose ? Elle soulève la couverture. Rien, seulement le drap tiède. Il est perdu ! Le sourire de Nina disparaît. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Nina pousse le tas d'un bras. Une tasse roule vers la chaise. Le tas retombe, plus mêlé. Ça ne marche pas. Dans sa poitrine, ça se bouscule. L'envie et l'inquiétude se heurtent. Maman s'accroupit à la même hauteur. Tu veux pousser, ou regarder ? Je veux mon ours. Nina baisse les épaules.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sami joue dans sa chambre. Maman plie des chaussettes. Sami a des peluches. Les peluches sont douces. Sami fait un pique-nique. Les tasses en bois font clic. Puis le jeu est fini. Maman dit : c'est l'heure de &lt;emphasis&gt;ranger&lt;/emphasis&gt;. Ranger, c'est mettre dans la caisse. Sami prend une peluche. Il la met dans la caisse. Il prend un livre. Il le met dans la caisse. Encore une peluche. Dans la caisse. La caisse est pleine. Le tapis est vide. Parce qu'il range, la chambre est calme. Maman dit : merci Sami. Sami ferme le couvercle. Ça fait toc. [pause]</t>
+          <t>La vapeur du cacao grimpe l'escalier. Elle entre dans la chambre froide. Sur la vitre, la pluie trace un chemin. La boîte à musique vient de se taire. Un ding reste coincé dans l'air. Sur le couvercle, une &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt;. Elle capte un bout de ciel gris. La lumière est basse, un peu bleue. Une chaussette sèche sur la chaise. Elle est un peu tiède. La chambre sent le cacao chaud. Il fait frais, ce soir. Le cacao est sur le feu. Je le veux sur le tapis ! Maintenant, maman. Il va refroidir vite. En ce moment, Nina s'agenouille. Le tapis est épais, un peu froid. Un ours brun attend sur l'oreiller. Toi, tu viens au pique-nique. Elle le pose au milieu du tapis. Un lapin gris la rejoint. Une poule jaune s'installe près de lui. Nina aligne trois tasses en bois. Les tasses font clic. C'est pour le vrai cacao. Il arrive, bien chaud. Vous soufflerez dessus. Nina souffle au-dessus d'une tasse. Ffff. Maman pousse la porte, une grande tasse à la main. Une petite vapeur danse au bord. Pose-la au milieu ! Nina cherche un rond libre. La patte du lapin occupe le centre. L'ours veut le cacao, lui. Où est ton ours, alors ? Nina se tourne vers l'oreiller. L'oreiller est plat, vide. Il n'est plus sur le lit. Sous la couverture rose ? Elle soulève la couverture. Rien, seulement le drap tiède. Il est perdu ! Le sourire de Nina disparaît. Les peluches et les tasses couvrent le tapis. Je n'ai pas de place. Nina pousse le tas d'un bras. Une tasse roule vers la chaise. Le tas retombe, plus mêlé. Ça ne marche pas. Dans sa poitrine, ça se bouscule. L'envie et l'inquiétude se heurtent. Maman s'accroupit à la même hauteur. Tu veux pousser, ou regarder ? Je veux mon ours. Nina baisse les épaules. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>lune d'étain</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,61 +1321,75 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller; emotion=impatience_curieuse; intensite=2; destinataire=enfant; sous_texte=la_lune_detain_sur_la_boite; tempo=naturel; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Trois notes sortent de la boîte à musique.
-narrateur|Ding.
-narrateur|Puis plus rien.
+          <t>narrateur|La vapeur du cacao grimpe l'escalier.
+narrateur|Elle entre dans la chambre froide.
+narrateur|Sur la vitre, la pluie trace un chemin.
+narrateur|La boîte à musique vient de se taire.
+narrateur|Un ding reste coincé dans l'air.
+narrateur|Sur le couvercle, une lune d'étain.
+narrateur|Elle capte un bout de ciel gris.
+narrateur|La lumière est basse, un peu bleue.
 narrateur|Une chaussette sèche sur la chaise.
-narrateur|Elle est encore un peu tiède.
-narrateur|Dehors, les feuilles sont mouillées.
+narrateur|Elle est un peu tiède.
+narrateur|La chambre sent le cacao chaud.
 papa|Il fait frais, ce soir.
 maman|Le cacao est sur le feu.
-narrateur|Dans la chambre, le tapis est épais.
-narrateur|Un ours en peluche attend sur l'oreiller.
-narrateur|Il est tout doux, un peu chaud.
-narrateur|En ce moment, Nina est à genoux.
-narrateur|Elle prend l'ours contre sa joue.
-enfant-f|Toi, tu viens au tapis.
-narrateur|Un lapin et une poule attendent déjà.
-narrateur|Nina pose trois tasses en bois.
+enfant-f|Je le veux sur le tapis !
+enfant-f|Maintenant, maman.
+maman|Il va refroidir vite.
+narrateur|En ce moment, Nina s'agenouille.
+narrateur|Le tapis est épais, un peu froid.
+narrateur|Un ours brun attend sur l'oreiller.
+enfant-f|Toi, tu viens au pique-nique.
+narrateur|Elle le pose au milieu du tapis.
+narrateur|Un lapin gris la rejoint.
+narrateur|Une poule jaune s'installe près de lui.
+narrateur|Nina aligne trois tasses en bois.
 narrateur|Les tasses font clic.
-enfant-f|C'est un pique-nique !
-maman|Un pique-nique pour les peluches.
-narrateur|Nina donne une tasse à l'ours.
-narrateur|Elle donne une tasse au lapin.
-narrateur|La poule a la petite tasse.
-papa|Ils sont bien installés.
-enfant-f|Ils boivent du cacao, papa.
-papa|Du cacao en bois, alors.
+enfant-f|C'est pour le vrai cacao.
+maman|Il arrive, bien chaud.
+papa|Vous soufflerez dessus.
 narrateur|Nina souffle au-dessus d'une tasse.
 enfant-f|Ffff.
-maman|Le vrai cacao arrive bientôt.
-enfant-f|On le boit ici, sur le tapis ?
-maman|Oui, au milieu, tout chaud.
-narrateur|Maman entre avec la grande tasse.
-narrateur|Ça sent le cacao, tout près.
-narrateur|Une petite vapeur monte.
-narrateur|Nina cherche un rond pour la tasse.
-narrateur|Une tasse en bois est déjà là.
-narrateur|La patte du lapin est dessus.
-enfant-f|L'ours veut le vrai cacao aussi.
-maman|Où est-il, ton ours ?
-narrateur|Nina regarde l'oreiller.
+narrateur|Maman pousse la porte, une grande tasse à la main.
+narrateur|Une petite vapeur danse au bord.
+enfant-f|Pose-la au milieu !
+narrateur|Nina cherche un rond libre.
+narrateur|La patte du lapin occupe le centre.
+enfant-f|L'ours veut le cacao, lui.
+maman|Où est ton ours, alors ?
+narrateur|Nina se tourne vers l'oreiller.
 narrateur|L'oreiller est plat, vide.
 enfant-f|Il n'est plus sur le lit.
-papa|Sous la couverture ?
-narrateur|Elle soulève la couverture rose.
+papa|Sous la couverture rose ?
+narrateur|Elle soulève la couverture.
 narrateur|Rien, seulement le drap tiède.
-enfant-f|Il est perdu.
+enfant-f|Il est perdu !
+narrateur|Le sourire de Nina disparaît.
 narrateur|Les peluches et les tasses couvrent le tapis.
 enfant-f|Je n'ai pas de place.
-maman|Il faut un petit rond, au milieu.
-narrateur|Nina prend une tasse en bois.
-narrateur|Elle la pose dans la caisse ronde.
-narrateur|Clic.
-enfant-f|Je cherche dessous.</t>
+narrateur|Nina pousse le tas d'un bras.
+narrateur|Une tasse roule vers la chaise.
+narrateur|Le tas retombe, plus mêlé.
+enfant-f|Ça ne marche pas.
+narrateur|Dans sa poitrine, ça se bouscule.
+narrateur|L'envie et l'inquiétude se heurtent.
+narrateur|Maman s'accroupit à la même hauteur.
+maman|Tu veux pousser, ou regarder ?
+enfant-f|Je veux mon ours.
+narrateur|Nina baisse les épaules.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,boite-musique</t>
         </is>
       </c>
     </row>
@@ -1402,17 +1416,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nina cherche son ours. Où est-il ?</t>
+          <t>Nina cherche son ours sous le tas. Où se cache-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nina cherche son ours. Où est-il ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina cherche son &lt;emphasis level="moderate"&gt;ours&lt;/emphasis&gt; sous le tas. Où se cache-t-il ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Après le jeu, que fait Sami ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina cherche son &lt;emphasis&gt;ours&lt;/emphasis&gt; sous le tas. Où se cache-t-il ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1475,7 +1489,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1486,7 +1500,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,34 +1515,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1543,23 +1561,23 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=l_ours_est_sous_le_tas; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nina cherche son ours.
-narrateur|Où est-il ?</t>
+          <t>narrateur|Nina cherche son ours sous le tas.
+maman|Où se cache-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1586,17 +1604,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>La deuxième tasse va dans la caisse. Clic. Nina prend le lapin tout doux. Elle le glisse dans la caisse. Tu regardes bien sous les peluches ? Oui, maman. La poule est encore au milieu. Un coin de tapis reparaît. Nina soulève la poule. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci, tu l'as trouvé. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.</t>
+          <t>J'arrête de pousser. Elle lâche le tas. Près de la fenêtre, la lune d'étain brille. Elle me montre le tapis. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. La tasse a sa place. La deuxième tasse suit. Toi aussi, lapin. Elle glisse le lapin dans la caisse. Tu regardes bien dessous ? Oui, maman. Un coin de tapis reparaît. La poule reste au milieu. Je prends tout d'un coup. Nina ouvre les deux mains. Elle veut vider le tapis vite. La poule bascule sur le côté. Puis la dernière tasse part sous la chaise. Oh non. Nina s'arrête net. Pas comme ça. Elle refuse de foncer. Elle lève les yeux vers la boîte. La lune d'étain capte la pluie. Un reflet tombe sur un petit dos. Là, sous la poule. Nina soulève la poule, sans se presser. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci d'avoir regardé, Nina. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>La deuxième tasse va dans la caisse. Clic. Nina prend le lapin tout doux. Elle le glisse dans la caisse. Tu regardes bien sous les peluches ? Oui, maman. La poule est encore au milieu. Un coin de tapis reparaît. Nina soulève la poule. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci, tu l'as trouvé. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'arrête de pousser. Elle lâche le tas. Près de la fenêtre, la &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; brille. Elle me montre le tapis. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. La tasse a sa place. La deuxième tasse suit. Toi aussi, lapin. Elle glisse le lapin dans la caisse. Tu regardes bien dessous ? Oui, maman. Un coin de tapis reparaît. La poule reste au milieu. Je prends tout d'un coup. Nina ouvre les deux mains. Elle veut vider le tapis vite. La poule bascule sur le côté. Puis la dernière tasse part sous la chaise. Oh non. Nina s'arrête net. Pas comme ça. Elle refuse de foncer. Elle lève les yeux vers la boîte. La lune d'étain capte la pluie. Un reflet tombe sur un petit dos. Là, sous la poule. Nina soulève la poule, sans se presser. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci d'avoir regardé, Nina. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Sami a rangé. Les peluches sont dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Maman est là. [pause]</t>
+          <t>J'arrête de pousser. Elle lâche le tas. Près de la fenêtre, la &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; brille. Elle me montre le tapis. Nina prend une tasse en bois. Elle la pose dans la caisse ronde. Clic. La tasse a sa place. La deuxième tasse suit. Toi aussi, lapin. Elle glisse le lapin dans la caisse. Tu regardes bien dessous ? Oui, maman. Un coin de tapis reparaît. La poule reste au milieu. Je prends tout d'un coup. Nina ouvre les deux mains. Elle veut vider le tapis vite. La poule bascule sur le côté. Puis la dernière tasse part sous la chaise. Oh non. Nina s'arrête net. Pas comme ça. Elle refuse de foncer. Elle lève les yeux vers la boîte. La lune d'étain capte la pluie. Un reflet tombe sur un petit dos. Là, sous la poule. Nina soulève la poule, sans se presser. Un museau brun est dessous. Mon ours ! L'ours était sous la poule. Une tasse en bois l'avait caché. Nina le serre contre sa joue. Le poil est chaud, un peu écrasé. Merci d'avoir regardé, Nina. Il buvait en dessous. Te voilà, petit ours. La dernière tasse va dans la caisse. Le tapis a un rond vide, au milieu. Nina pose l'ours contre son genou. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1643,7 +1661,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1651,10 +1669,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,30 +1695,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>lune d'étain</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1709,10 +1727,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1725,27 +1743,47 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_suit_la_lune_trouve_l_ours; tempo=naturel; sourire=franc; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|La deuxième tasse va dans la caisse.
+          <t>enfant-f|J'arrête de pousser.
+narrateur|Elle lâche le tas.
+narrateur|Près de la fenêtre, la lune d'étain brille.
+enfant-f|Elle me montre le tapis.
+narrateur|Nina prend une tasse en bois.
+narrateur|Elle la pose dans la caisse ronde.
 narrateur|Clic.
-narrateur|Nina prend le lapin tout doux.
-narrateur|Elle le glisse dans la caisse.
-maman|Tu regardes bien sous les peluches ?
+papa|La tasse a sa place.
+narrateur|La deuxième tasse suit.
+enfant-f|Toi aussi, lapin.
+narrateur|Elle glisse le lapin dans la caisse.
+maman|Tu regardes bien dessous ?
 enfant-f|Oui, maman.
-narrateur|La poule est encore au milieu.
-papa|Un coin de tapis reparaît.
-narrateur|Nina soulève la poule.
+narrateur|Un coin de tapis reparaît.
+narrateur|La poule reste au milieu.
+enfant-f|Je prends tout d'un coup.
+narrateur|Nina ouvre les deux mains.
+narrateur|Elle veut vider le tapis vite.
+narrateur|La poule bascule sur le côté.
+narrateur|Puis la dernière tasse part sous la chaise.
+enfant-f|Oh non.
+narrateur|Nina s'arrête net.
+enfant-f|Pas comme ça.
+narrateur|Elle refuse de foncer.
+narrateur|Elle lève les yeux vers la boîte.
+narrateur|La lune d'étain capte la pluie.
+narrateur|Un reflet tombe sur un petit dos.
+enfant-f|Là, sous la poule.
+narrateur|Nina soulève la poule, sans se presser.
 narrateur|Un museau brun est dessous.
 enfant-f|Mon ours !
 narrateur|L'ours était sous la poule.
 narrateur|Une tasse en bois l'avait caché.
 narrateur|Nina le serre contre sa joue.
 narrateur|Le poil est chaud, un peu écrasé.
-papa|Merci, tu l'as trouvé.
+papa|Merci d'avoir regardé, Nina.
 enfant-f|Il buvait en dessous.
 maman|Te voilà, petit ours.
 narrateur|La dernière tasse va dans la caisse.
@@ -1753,6 +1791,11 @@
 narrateur|Nina pose l'ours contre son genou.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>tasse-bois,caisse</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,17 +1820,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la vraie tasse au milieu. La vapeur sent le cacao. Il est chaud. On souffle un peu. Nina souffle. Ffff. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu veux encore un peu ? Oui, maman. La pluie tapote plus doucement. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. On est bien, ici.</t>
+          <t>Maman avance la vraie tasse. La vapeur sent le cacao. Je la prends maintenant ! Nina tend les deux mains trop vite. La tasse penche, la vapeur fuit. Elle est chaude, tu vois ? J'attends. Nina pose les mains à plat. Elle souffle une fois, puis deux. Ffff. La lune d'étain éclaire un rond. Là, au milieu. Maman pose la tasse sur ce rond. On souffle un peu. Nina souffle avec lui. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu en veux un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la vraie tasse au milieu. La vapeur sent le cacao. Il est chaud. On souffle un peu. Nina souffle. Ffff. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu veux encore un peu ? Oui, maman. La pluie tapote plus doucement. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. On est bien, ici.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Maman avance la vraie tasse. La vapeur sent le cacao. Je la prends maintenant ! Nina tend les deux mains trop vite. La tasse penche, la vapeur fuit. Elle est chaude, tu vois ? J'attends. Nina pose les mains à plat. Elle souffle une fois, puis deux. Ffff. La &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt; éclaire un rond. Là, au milieu. Maman pose la tasse sur ce rond. On souffle un peu. Nina souffle avec lui. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu en veux un peu ? Oui, maman.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Sami ferme la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Maman lui tend l'eau. [pause]</t>
+          <t>&lt;low-pitch&gt;Maman avance la vraie tasse. La vapeur sent le cacao. Je la prends maintenant ! Nina tend les deux mains trop vite. La tasse penche, la vapeur fuit. Elle est chaude, tu vois ? J'attends. Nina pose les mains à plat. Elle souffle une fois, puis deux. Ffff. La &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt; éclaire un rond. Là, au milieu. Maman pose la tasse sur ce rond. On souffle un peu. Nina souffle avec lui. Elle boit une petite gorgée. Le cacao est doux, un peu sucré. L'ours a une goutte, papa. Une toute petite goutte. Tu en veux un peu ? Oui, maman.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1834,7 +1877,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1842,22 +1885,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1868,30 +1915,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>lune d'étain</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1900,40 +1947,53 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=deux_envies_qui_se_heurtent; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_pose_la_tasse; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose la vraie tasse au milieu.
+          <t>narrateur|Maman avance la vraie tasse.
 narrateur|La vapeur sent le cacao.
-enfant-f|Il est chaud.
+enfant-f|Je la prends maintenant !
+narrateur|Nina tend les deux mains trop vite.
+narrateur|La tasse penche, la vapeur fuit.
+maman|Elle est chaude, tu vois ?
+enfant-f|J'attends.
+narrateur|Nina pose les mains à plat.
+narrateur|Elle souffle une fois, puis deux.
+enfant-f|Ffff.
+narrateur|La lune d'étain éclaire un rond.
+enfant-f|Là, au milieu.
+narrateur|Maman pose la tasse sur ce rond.
 papa|On souffle un peu.
-narrateur|Nina souffle.
-narrateur|Ffff.
+narrateur|Nina souffle avec lui.
 narrateur|Elle boit une petite gorgée.
 narrateur|Le cacao est doux, un peu sucré.
 enfant-f|L'ours a une goutte, papa.
 papa|Une toute petite goutte.
-maman|Tu veux encore un peu ?
-enfant-f|Oui, maman.
-narrateur|La pluie tapote plus doucement.
-narrateur|La chaussette sur la chaise est sèche.
-narrateur|Nina tient l'ours d'une main.
-narrateur|De l'autre, elle tient la tasse.
-maman|On est bien, ici.</t>
+maman|Tu en veux un peu ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>cacao</t>
         </is>
       </c>
     </row>
@@ -1960,17 +2020,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'ours a bu du cacao. Toi aussi. Bravo, tu l'as retrouvé. La vapeur s'en va tout doux. Le tapis reste chaud sous les genoux.</t>
+          <t>La pluie tapote plus bas. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. La boîte à musique reprend un ding. On est bien, ici. Oui, vous y êtes. La vapeur s'accroche à la lune d'étain.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'ours a bu du cacao. Toi aussi. Bravo, tu l'as retrouvé. La vapeur s'en va tout doux. Le tapis reste chaud sous les genoux.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La pluie tapote plus bas. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. La boîte à musique reprend un ding. On est bien, ici. Oui, vous y êtes. La vapeur s'accroche à la &lt;emphasis level="moderate"&gt;lune d'étain&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La pluie tapote plus bas. La chaussette sur la chaise est sèche. Nina tient l'ours d'une main. De l'autre, elle tient la tasse. La boîte à musique reprend un ding. On est bien, ici. Oui, vous y êtes. La vapeur s'accroche à la &lt;emphasis&gt;lune d'étain&lt;/emphasis&gt;.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2017,18 +2077,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2037,12 +2097,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2051,17 +2111,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>lune d'étain</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2070,11 +2134,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2083,28 +2147,40 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=la_vapeur_s_accroche_a_la_lune_detain; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|L'ours a bu du cacao.
-maman|Toi aussi.
-papa|Bravo, tu l'as retrouvé.
-narrateur|La vapeur s'en va tout doux.
-narrateur|Le tapis reste chaud sous les genoux.</t>
+          <t>narrateur|La pluie tapote plus bas.
+narrateur|La chaussette sur la chaise est sèche.
+narrateur|Nina tient l'ours d'une main.
+narrateur|De l'autre, elle tient la tasse.
+narrateur|La boîte à musique reprend un ding.
+enfant-f|On est bien, ici.
+maman|Oui, vous y êtes.
+narrateur|La vapeur s'accroche à la lune d'étain.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>pluie,boite-musique</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2189,6 +2265,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
